--- a/Employee_Reports_wi52/Renato Dimalanta Canlas Q0274.xlsx
+++ b/Employee_Reports_wi52/Renato Dimalanta Canlas Q0274.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1598,11 +1598,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1647,11 +1647,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1684,11 +1684,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1721,11 +1721,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
